--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -811,769 +811,775 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.2146,0.7010,0.0263,0.0805</t>
-  </si>
-  <si>
-    <t>0.0007,0.0235,0.0001,0.9986</t>
-  </si>
-  <si>
-    <t>0.4474,0.4249,0.0216,0.0638</t>
-  </si>
-  <si>
-    <t>0.0095,0.0760,0.0007,0.9816</t>
-  </si>
-  <si>
-    <t>0.3805,0.7270,0.0221,0.0018</t>
-  </si>
-  <si>
-    <t>0.3928,0.7192,0.0157,0.0018</t>
-  </si>
-  <si>
-    <t>0.3978,0.7079,0.0189,0.0022</t>
-  </si>
-  <si>
-    <t>0.4686,0.6602,0.0124,0.0017</t>
-  </si>
-  <si>
-    <t>0.4372,0.6801,0.0143,0.0020</t>
-  </si>
-  <si>
-    <t>0.4142,0.7103,0.0135,0.0016</t>
-  </si>
-  <si>
-    <t>0.4495,0.6810,0.0114,0.0015</t>
-  </si>
-  <si>
-    <t>0.4515,0.6656,0.0187,0.0020</t>
-  </si>
-  <si>
-    <t>0.0286,0.9493,0.0356,0.0039</t>
-  </si>
-  <si>
-    <t>0.0354,0.6991,0.6137,0.0039</t>
-  </si>
-  <si>
-    <t>0.0704,0.6254,0.5508,0.0062</t>
-  </si>
-  <si>
-    <t>0.0800,0.7936,0.2226,0.0122</t>
-  </si>
-  <si>
-    <t>0.1324,0.7598,0.1200,0.0580</t>
-  </si>
-  <si>
-    <t>0.0013,0.9957,0.0114,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.9920,0.0199,0.0001</t>
-  </si>
-  <si>
-    <t>0.0332,0.9636,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.0036,0.9910,0.0182,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9960,0.0113,0.0000</t>
-  </si>
-  <si>
-    <t>0.0499,0.6688,0.5128,0.0489</t>
-  </si>
-  <si>
-    <t>0.1419,0.4779,0.4999,0.0212</t>
-  </si>
-  <si>
-    <t>0.0243,0.3431,0.8710,0.0080</t>
-  </si>
-  <si>
-    <t>0.0357,0.7307,0.5222,0.0111</t>
-  </si>
-  <si>
-    <t>0.0256,0.1576,0.9221,0.0034</t>
-  </si>
-  <si>
-    <t>0.1983,0.0865,0.7289,0.0084</t>
-  </si>
-  <si>
-    <t>0.0071,0.0577,0.9805,0.0017</t>
-  </si>
-  <si>
-    <t>0.0340,0.9388,0.0692,0.0011</t>
-  </si>
-  <si>
-    <t>0.3099,0.7167,0.0615,0.0064</t>
-  </si>
-  <si>
-    <t>0.0005,0.1049,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.9757,0.0815,0.0003</t>
-  </si>
-  <si>
-    <t>0.0898,0.8968,0.0308,0.0058</t>
-  </si>
-  <si>
-    <t>0.0693,0.8537,0.1956,0.0034</t>
-  </si>
-  <si>
-    <t>0.0374,0.9576,0.0219,0.0004</t>
-  </si>
-  <si>
-    <t>0.0047,0.9884,0.0200,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.1281,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9373,0.2772,0.0132</t>
-  </si>
-  <si>
-    <t>0.0024,0.9786,0.1781,0.0007</t>
-  </si>
-  <si>
-    <t>0.0035,0.6399,0.9353,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.9820,0.1805,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9457,0.8673,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.9156,0.0017,0.6732</t>
-  </si>
-  <si>
-    <t>0.0003,0.9981,0.0108,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9985,0.0168,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9813,0.7290,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9807,0.6419,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.5170,0.8938,0.0034</t>
-  </si>
-  <si>
-    <t>0.1633,0.0276,0.8164,0.0107</t>
-  </si>
-  <si>
-    <t>0.0005,0.6023,0.9835,0.0001</t>
-  </si>
-  <si>
-    <t>0.0060,0.8807,0.6515,0.0021</t>
-  </si>
-  <si>
-    <t>0.2700,0.8082,0.0204,0.0018</t>
-  </si>
-  <si>
-    <t>0.3807,0.6826,0.0399,0.0045</t>
-  </si>
-  <si>
-    <t>0.3187,0.7571,0.0178,0.0033</t>
-  </si>
-  <si>
-    <t>0.0040,0.5646,0.9651,0.0008</t>
-  </si>
-  <si>
-    <t>0.4887,0.6219,0.0161,0.0027</t>
-  </si>
-  <si>
-    <t>0.3647,0.7441,0.0135,0.0020</t>
-  </si>
-  <si>
-    <t>0.2033,0.8599,0.0113,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.3473,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9225,0.6065,0.0011</t>
-  </si>
-  <si>
-    <t>0.0037,0.9257,0.5623,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.3677,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.7446,0.9220,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.9919,0.0095,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.4318,0.3114,0.3199,0.0132</t>
-  </si>
-  <si>
-    <t>0.0743,0.8966,0.0759,0.0024</t>
-  </si>
-  <si>
-    <t>0.0069,0.7524,0.8638,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.3426,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9961,0.0488,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0282,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.1094,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0070,0.0004,0.9982</t>
-  </si>
-  <si>
-    <t>0.0001,0.0168,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0002,0.0092,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0007,0.0178,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0005,0.0226,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0002,0.0153,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.9981,0.0501,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.1881,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9944,0.1461,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9981,0.1271,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9974,0.0954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.4650,0.0000</t>
-  </si>
-  <si>
-    <t>0.3662,0.7314,0.0279,0.0017</t>
-  </si>
-  <si>
-    <t>0.3287,0.7734,0.0163,0.0013</t>
-  </si>
-  <si>
-    <t>0.2684,0.8154,0.0168,0.0016</t>
-  </si>
-  <si>
-    <t>0.2930,0.7906,0.0228,0.0020</t>
-  </si>
-  <si>
-    <t>0.3076,0.7861,0.0221,0.0014</t>
-  </si>
-  <si>
-    <t>0.3551,0.7518,0.0148,0.0017</t>
-  </si>
-  <si>
-    <t>0.2675,0.8176,0.0171,0.0013</t>
-  </si>
-  <si>
-    <t>0.3641,0.7266,0.0275,0.0025</t>
-  </si>
-  <si>
-    <t>0.5371,0.5757,0.0129,0.0025</t>
-  </si>
-  <si>
-    <t>0.4040,0.7109,0.0157,0.0018</t>
-  </si>
-  <si>
-    <t>0.4135,0.7061,0.0173,0.0016</t>
-  </si>
-  <si>
-    <t>0.4914,0.6351,0.0145,0.0018</t>
-  </si>
-  <si>
-    <t>0.4482,0.6870,0.0134,0.0012</t>
-  </si>
-  <si>
-    <t>0.4716,0.6638,0.0138,0.0014</t>
-  </si>
-  <si>
-    <t>0.5479,0.5754,0.0118,0.0019</t>
-  </si>
-  <si>
-    <t>0.4915,0.6298,0.0096,0.0021</t>
-  </si>
-  <si>
-    <t>0.0038,0.0907,0.9863,0.0006</t>
-  </si>
-  <si>
-    <t>0.0378,0.5997,0.6921,0.0082</t>
-  </si>
-  <si>
-    <t>0.2372,0.5319,0.1066,0.1560</t>
-  </si>
-  <si>
-    <t>0.0703,0.1493,0.8438,0.0146</t>
-  </si>
-  <si>
-    <t>0.0082,0.9852,0.0149,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.9914,0.0126,0.0001</t>
-  </si>
-  <si>
-    <t>0.0382,0.9524,0.0270,0.0006</t>
-  </si>
-  <si>
-    <t>0.0349,0.9572,0.0268,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.9948,0.0133,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9949,0.0073,0.0000</t>
-  </si>
-  <si>
-    <t>0.0787,0.9273,0.0208,0.0009</t>
-  </si>
-  <si>
-    <t>0.1286,0.4817,0.5304,0.0124</t>
-  </si>
-  <si>
-    <t>0.1264,0.3518,0.6184,0.0178</t>
-  </si>
-  <si>
-    <t>0.0772,0.8289,0.1500,0.0181</t>
-  </si>
-  <si>
-    <t>0.0715,0.6707,0.2982,0.1269</t>
-  </si>
-  <si>
-    <t>0.0046,0.4995,0.0017,0.9380</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0079,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0082,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9979,0.0105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0248,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.9890,0.0165,0.0001</t>
-  </si>
-  <si>
-    <t>0.0420,0.9521,0.0267,0.0004</t>
-  </si>
-  <si>
-    <t>0.0484,0.9454,0.0293,0.0005</t>
-  </si>
-  <si>
-    <t>0.2521,0.7771,0.0643,0.0027</t>
-  </si>
-  <si>
-    <t>0.6200,0.4152,0.0111,0.0074</t>
-  </si>
-  <si>
-    <t>0.4820,0.6215,0.0161,0.0030</t>
-  </si>
-  <si>
-    <t>0.3496,0.7113,0.0478,0.0050</t>
-  </si>
-  <si>
-    <t>0.5185,0.5718,0.0175,0.0039</t>
-  </si>
-  <si>
-    <t>0.2889,0.7734,0.0424,0.0018</t>
-  </si>
-  <si>
-    <t>0.4443,0.6647,0.0172,0.0030</t>
-  </si>
-  <si>
-    <t>0.5300,0.5988,0.0150,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.9946,0.3019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9846,0.4618,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.9589,0.4965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0045,0.9095,0.6119,0.0007</t>
-  </si>
-  <si>
-    <t>0.0754,0.7788,0.0840,0.2118</t>
-  </si>
-  <si>
-    <t>0.1121,0.7317,0.2350,0.0324</t>
-  </si>
-  <si>
-    <t>0.1350,0.1935,0.5604,0.1752</t>
-  </si>
-  <si>
-    <t>0.2048,0.7452,0.0794,0.0291</t>
-  </si>
-  <si>
-    <t>0.0045,0.0592,0.0006,0.9916</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0243,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0008,0.0020,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.2531,0.0000</t>
-  </si>
-  <si>
-    <t>0.4041,0.6923,0.0172,0.0035</t>
-  </si>
-  <si>
-    <t>0.0304,0.9679,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.4894,0.5597,0.0258,0.0088</t>
-  </si>
-  <si>
-    <t>0.0435,0.9547,0.0142,0.0007</t>
-  </si>
-  <si>
-    <t>0.4197,0.6648,0.0231,0.0053</t>
-  </si>
-  <si>
-    <t>0.1154,0.2825,0.0065,0.6513</t>
-  </si>
-  <si>
-    <t>0.7226,0.3351,0.0141,0.0027</t>
-  </si>
-  <si>
-    <t>0.0035,0.9176,0.7007,0.0010</t>
-  </si>
-  <si>
-    <t>0.4854,0.3075,0.0895,0.0906</t>
-  </si>
-  <si>
-    <t>0.6352,0.4151,0.0214,0.0049</t>
-  </si>
-  <si>
-    <t>0.0266,0.9656,0.0160,0.0006</t>
-  </si>
-  <si>
-    <t>0.0880,0.9114,0.0192,0.0033</t>
-  </si>
-  <si>
-    <t>0.1583,0.8526,0.0356,0.0048</t>
-  </si>
-  <si>
-    <t>0.0150,0.9679,0.0408,0.0010</t>
-  </si>
-  <si>
-    <t>0.1114,0.8423,0.1184,0.0044</t>
-  </si>
-  <si>
-    <t>0.0973,0.8874,0.0402,0.0053</t>
-  </si>
-  <si>
-    <t>0.5701,0.5343,0.0171,0.0025</t>
-  </si>
-  <si>
-    <t>0.7093,0.3798,0.0091,0.0020</t>
-  </si>
-  <si>
-    <t>0.3822,0.7211,0.0215,0.0023</t>
-  </si>
-  <si>
-    <t>0.6033,0.4556,0.0129,0.0052</t>
-  </si>
-  <si>
-    <t>0.4365,0.6672,0.0117,0.0029</t>
-  </si>
-  <si>
-    <t>0.4977,0.6106,0.0126,0.0029</t>
-  </si>
-  <si>
-    <t>0.6387,0.4347,0.0153,0.0035</t>
-  </si>
-  <si>
-    <t>0.6065,0.4710,0.0093,0.0039</t>
-  </si>
-  <si>
-    <t>0.0244,0.9675,0.0173,0.0006</t>
-  </si>
-  <si>
-    <t>0.0817,0.9351,0.0137,0.0005</t>
-  </si>
-  <si>
-    <t>0.0700,0.9379,0.0165,0.0005</t>
-  </si>
-  <si>
-    <t>0.0519,0.6538,0.7017,0.0022</t>
-  </si>
-  <si>
-    <t>0.2116,0.8411,0.0254,0.0018</t>
-  </si>
-  <si>
-    <t>0.2092,0.8400,0.0231,0.0022</t>
-  </si>
-  <si>
-    <t>0.2404,0.8171,0.0310,0.0020</t>
-  </si>
-  <si>
-    <t>0.1913,0.8466,0.0286,0.0026</t>
-  </si>
-  <si>
-    <t>0.0037,0.4678,0.9754,0.0004</t>
-  </si>
-  <si>
-    <t>0.2541,0.7852,0.0452,0.0048</t>
-  </si>
-  <si>
-    <t>0.0003,0.9009,0.9477,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9581,0.7831,0.0001</t>
-  </si>
-  <si>
-    <t>0.0361,0.0768,0.9354,0.0017</t>
-  </si>
-  <si>
-    <t>0.0005,0.9756,0.6629,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.6476,0.9684,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0095,0.9962,0.0017</t>
-  </si>
-  <si>
-    <t>0.0071,0.0859,0.9782,0.0010</t>
-  </si>
-  <si>
-    <t>0.0547,0.4143,0.7522,0.0085</t>
-  </si>
-  <si>
-    <t>0.0932,0.7959,0.1604,0.0319</t>
-  </si>
-  <si>
-    <t>0.0716,0.8638,0.1142,0.0114</t>
-  </si>
-  <si>
-    <t>0.0224,0.9467,0.0704,0.0016</t>
-  </si>
-  <si>
-    <t>0.0136,0.9659,0.0288,0.0070</t>
-  </si>
-  <si>
-    <t>0.0339,0.9113,0.1163,0.0059</t>
-  </si>
-  <si>
-    <t>0.2605,0.6266,0.1192,0.0380</t>
-  </si>
-  <si>
-    <t>0.0492,0.9106,0.0753,0.0050</t>
-  </si>
-  <si>
-    <t>0.1202,0.8987,0.0230,0.0014</t>
-  </si>
-  <si>
-    <t>0.0425,0.9519,0.0241,0.0005</t>
-  </si>
-  <si>
-    <t>0.1276,0.8981,0.0220,0.0008</t>
-  </si>
-  <si>
-    <t>0.1575,0.8867,0.0138,0.0010</t>
-  </si>
-  <si>
-    <t>0.0595,0.9467,0.0126,0.0006</t>
-  </si>
-  <si>
-    <t>0.0210,0.9529,0.0501,0.0053</t>
-  </si>
-  <si>
-    <t>0.1427,0.6692,0.2646,0.0261</t>
-  </si>
-  <si>
-    <t>0.1137,0.7366,0.0762,0.1805</t>
-  </si>
-  <si>
-    <t>0.0836,0.7531,0.2205,0.0611</t>
-  </si>
-  <si>
-    <t>0.3535,0.2119,0.4218,0.0354</t>
-  </si>
-  <si>
-    <t>0.0076,0.2987,0.9481,0.0027</t>
-  </si>
-  <si>
-    <t>0.0024,0.9823,0.1165,0.0009</t>
-  </si>
-  <si>
-    <t>0.0013,0.9781,0.3132,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.9745,0.2242,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9781,0.2208,0.0011</t>
-  </si>
-  <si>
-    <t>0.2949,0.7902,0.0216,0.0019</t>
-  </si>
-  <si>
-    <t>0.2845,0.7989,0.0150,0.0019</t>
-  </si>
-  <si>
-    <t>0.3233,0.7665,0.0129,0.0024</t>
-  </si>
-  <si>
-    <t>0.4348,0.6812,0.0111,0.0023</t>
-  </si>
-  <si>
-    <t>0.2464,0.8307,0.0149,0.0014</t>
-  </si>
-  <si>
-    <t>0.3544,0.7293,0.0288,0.0031</t>
-  </si>
-  <si>
-    <t>0.2833,0.8002,0.0200,0.0017</t>
-  </si>
-  <si>
-    <t>0.3127,0.7679,0.0172,0.0027</t>
-  </si>
-  <si>
-    <t>0.0250,0.5612,0.8258,0.0027</t>
-  </si>
-  <si>
-    <t>0.0751,0.8984,0.0586,0.0035</t>
-  </si>
-  <si>
-    <t>0.1952,0.7605,0.0487,0.0373</t>
-  </si>
-  <si>
-    <t>0.0028,0.6631,0.9365,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.7573,0.9762,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.9312,0.6264,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.3258,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0124,0.8541,0.5414,0.0029</t>
-  </si>
-  <si>
-    <t>0.0001,0.7436,0.9938,0.0000</t>
-  </si>
-  <si>
-    <t>0.0126,0.7798,0.6966,0.0028</t>
-  </si>
-  <si>
-    <t>0.0354,0.7207,0.5595,0.0129</t>
-  </si>
-  <si>
-    <t>0.2137,0.4363,0.3948,0.0202</t>
-  </si>
-  <si>
-    <t>0.2536,0.4400,0.1922,0.1063</t>
-  </si>
-  <si>
-    <t>0.4157,0.2774,0.2814,0.0260</t>
-  </si>
-  <si>
-    <t>0.1947,0.8628,0.0163,0.0010</t>
-  </si>
-  <si>
-    <t>0.3738,0.7301,0.0218,0.0020</t>
-  </si>
-  <si>
-    <t>0.5175,0.6182,0.0078,0.0016</t>
-  </si>
-  <si>
-    <t>0.3392,0.7624,0.0166,0.0017</t>
-  </si>
-  <si>
-    <t>0.3116,0.7797,0.0076,0.0023</t>
-  </si>
-  <si>
-    <t>0.3247,0.7752,0.0169,0.0015</t>
-  </si>
-  <si>
-    <t>0.3238,0.7848,0.0136,0.0012</t>
-  </si>
-  <si>
-    <t>0.2481,0.8190,0.0246,0.0014</t>
-  </si>
-  <si>
-    <t>0.0058,0.9650,0.1538,0.0019</t>
-  </si>
-  <si>
-    <t>0.0011,0.9345,0.7723,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.9507,0.7542,0.0002</t>
-  </si>
-  <si>
-    <t>0.0085,0.8946,0.5150,0.0013</t>
-  </si>
-  <si>
-    <t>0.0046,0.4017,0.9527,0.0017</t>
-  </si>
-  <si>
-    <t>0.0587,0.2709,0.3312,0.5292</t>
-  </si>
-  <si>
-    <t>0.0528,0.7983,0.2213,0.0776</t>
-  </si>
-  <si>
-    <t>0.0153,0.8531,0.4842,0.0040</t>
-  </si>
-  <si>
-    <t>0.3728,0.3589,0.0120,0.1428</t>
-  </si>
-  <si>
-    <t>0.0005,0.1440,0.0004,0.9973</t>
-  </si>
-  <si>
-    <t>0.0026,0.0341,0.0002,0.9954</t>
-  </si>
-  <si>
-    <t>0.0002,0.0020,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0059,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0186,0.8536,0.0027,0.3880</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.2782,0.6822,0.0249,0.0386</t>
+  </si>
+  <si>
+    <t>0.0010,0.0459,0.0001,0.9974</t>
+  </si>
+  <si>
+    <t>0.0600,0.5033,0.0025,0.5495</t>
+  </si>
+  <si>
+    <t>0.0050,0.1389,0.0004,0.9825</t>
+  </si>
+  <si>
+    <t>0.4651,0.6635,0.0153,0.0016</t>
+  </si>
+  <si>
+    <t>0.5400,0.5886,0.0098,0.0017</t>
+  </si>
+  <si>
+    <t>0.4208,0.6950,0.0162,0.0019</t>
+  </si>
+  <si>
+    <t>0.5134,0.6232,0.0105,0.0015</t>
+  </si>
+  <si>
+    <t>0.5361,0.5920,0.0131,0.0018</t>
+  </si>
+  <si>
+    <t>0.5567,0.5768,0.0104,0.0017</t>
+  </si>
+  <si>
+    <t>0.5774,0.5538,0.0112,0.0015</t>
+  </si>
+  <si>
+    <t>0.4791,0.6570,0.0141,0.0014</t>
+  </si>
+  <si>
+    <t>0.0704,0.8760,0.1096,0.0045</t>
+  </si>
+  <si>
+    <t>0.0469,0.6762,0.5554,0.0050</t>
+  </si>
+  <si>
+    <t>0.0029,0.8090,0.8901,0.0003</t>
+  </si>
+  <si>
+    <t>0.0429,0.4657,0.7661,0.0077</t>
+  </si>
+  <si>
+    <t>0.3098,0.4190,0.2897,0.0365</t>
+  </si>
+  <si>
+    <t>0.0006,0.9973,0.0106,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9934,0.0204,0.0000</t>
+  </si>
+  <si>
+    <t>0.0326,0.9626,0.0153,0.0005</t>
+  </si>
+  <si>
+    <t>0.0038,0.9899,0.0205,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9964,0.0125,0.0000</t>
+  </si>
+  <si>
+    <t>0.0668,0.7277,0.3399,0.0486</t>
+  </si>
+  <si>
+    <t>0.0620,0.6217,0.5639,0.0114</t>
+  </si>
+  <si>
+    <t>0.0230,0.5462,0.8006,0.0050</t>
+  </si>
+  <si>
+    <t>0.0835,0.3971,0.6811,0.0183</t>
+  </si>
+  <si>
+    <t>0.0108,0.4211,0.9124,0.0011</t>
+  </si>
+  <si>
+    <t>0.1030,0.4518,0.6034,0.0131</t>
+  </si>
+  <si>
+    <t>0.0128,0.1843,0.9505,0.0018</t>
+  </si>
+  <si>
+    <t>0.0378,0.9412,0.0504,0.0010</t>
+  </si>
+  <si>
+    <t>0.2069,0.8102,0.0521,0.0046</t>
+  </si>
+  <si>
+    <t>0.0010,0.0853,0.9950,0.0010</t>
+  </si>
+  <si>
+    <t>0.0033,0.9865,0.0646,0.0001</t>
+  </si>
+  <si>
+    <t>0.2049,0.8234,0.0160,0.0079</t>
+  </si>
+  <si>
+    <t>0.1729,0.7623,0.1366,0.0090</t>
+  </si>
+  <si>
+    <t>0.0667,0.9394,0.0169,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.9887,0.0173,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9976,0.0875,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.9032,0.5357,0.0052</t>
+  </si>
+  <si>
+    <t>0.0021,0.9854,0.0963,0.0005</t>
+  </si>
+  <si>
+    <t>0.0159,0.6061,0.8014,0.0137</t>
+  </si>
+  <si>
+    <t>0.0023,0.9791,0.1804,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0162,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.8645,0.7886,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.8920,0.0022,0.6960</t>
+  </si>
+  <si>
+    <t>0.0005,0.9972,0.0136,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0169,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0138,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9846,0.6139,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9915,0.3654,0.0000</t>
+  </si>
+  <si>
+    <t>0.0564,0.6887,0.4580,0.0180</t>
+  </si>
+  <si>
+    <t>0.1786,0.0543,0.7750,0.0092</t>
+  </si>
+  <si>
+    <t>0.0019,0.3862,0.9782,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9567,0.6330,0.0002</t>
+  </si>
+  <si>
+    <t>0.2328,0.8316,0.0219,0.0017</t>
+  </si>
+  <si>
+    <t>0.3936,0.6351,0.0742,0.0063</t>
+  </si>
+  <si>
+    <t>0.2097,0.8417,0.0162,0.0024</t>
+  </si>
+  <si>
+    <t>0.0027,0.8807,0.8733,0.0003</t>
+  </si>
+  <si>
+    <t>0.4149,0.6913,0.0133,0.0028</t>
+  </si>
+  <si>
+    <t>0.3041,0.7954,0.0113,0.0014</t>
+  </si>
+  <si>
+    <t>0.1980,0.8660,0.0116,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.2936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9478,0.5971,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9828,0.0652,0.0119</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.1919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.6773,0.9569,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9959,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.4685,0.2764,0.2697,0.0242</t>
+  </si>
+  <si>
+    <t>0.1440,0.7721,0.1738,0.0047</t>
+  </si>
+  <si>
+    <t>0.0055,0.8618,0.7609,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9953,0.0624,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0176,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0400,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0076,0.0006,0.9969</t>
+  </si>
+  <si>
+    <t>0.0001,0.0146,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.0339,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0011,0.0080,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.0003,0.0257,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.9964,0.1529,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9982,0.0589,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9957,0.1208,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9950,0.2227,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9980,0.0496,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9968,0.1355,0.0000</t>
+  </si>
+  <si>
+    <t>0.4255,0.6966,0.0141,0.0016</t>
+  </si>
+  <si>
+    <t>0.2178,0.8161,0.0510,0.0013</t>
+  </si>
+  <si>
+    <t>0.2690,0.8123,0.0191,0.0015</t>
+  </si>
+  <si>
+    <t>0.3505,0.7435,0.0185,0.0025</t>
+  </si>
+  <si>
+    <t>0.2580,0.8163,0.0213,0.0017</t>
+  </si>
+  <si>
+    <t>0.4478,0.6737,0.0153,0.0020</t>
+  </si>
+  <si>
+    <t>0.3208,0.7748,0.0188,0.0018</t>
+  </si>
+  <si>
+    <t>0.3545,0.7429,0.0205,0.0020</t>
+  </si>
+  <si>
+    <t>0.7315,0.3476,0.0099,0.0019</t>
+  </si>
+  <si>
+    <t>0.3742,0.7345,0.0175,0.0017</t>
+  </si>
+  <si>
+    <t>0.5840,0.5365,0.0090,0.0019</t>
+  </si>
+  <si>
+    <t>0.5988,0.4969,0.0153,0.0028</t>
+  </si>
+  <si>
+    <t>0.4350,0.6857,0.0126,0.0018</t>
+  </si>
+  <si>
+    <t>0.3456,0.7669,0.0139,0.0013</t>
+  </si>
+  <si>
+    <t>0.6618,0.4547,0.0072,0.0017</t>
+  </si>
+  <si>
+    <t>0.5218,0.6057,0.0106,0.0018</t>
+  </si>
+  <si>
+    <t>0.0058,0.1770,0.9690,0.0025</t>
+  </si>
+  <si>
+    <t>0.0634,0.4955,0.6675,0.0121</t>
+  </si>
+  <si>
+    <t>0.4285,0.2800,0.2558,0.0422</t>
+  </si>
+  <si>
+    <t>0.0251,0.3407,0.8701,0.0057</t>
+  </si>
+  <si>
+    <t>0.0055,0.9894,0.0113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.9908,0.0109,0.0001</t>
+  </si>
+  <si>
+    <t>0.0318,0.9576,0.0288,0.0006</t>
+  </si>
+  <si>
+    <t>0.0393,0.9546,0.0228,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.9934,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9968,0.0061,0.0000</t>
+  </si>
+  <si>
+    <t>0.0965,0.9103,0.0255,0.0016</t>
+  </si>
+  <si>
+    <t>0.0909,0.8134,0.1522,0.0104</t>
+  </si>
+  <si>
+    <t>0.1328,0.4651,0.4972,0.0271</t>
+  </si>
+  <si>
+    <t>0.0233,0.9252,0.1192,0.0134</t>
+  </si>
+  <si>
+    <t>0.0618,0.7571,0.3394,0.0139</t>
+  </si>
+  <si>
+    <t>0.0722,0.7733,0.1096,0.2303</t>
+  </si>
+  <si>
+    <t>0.0003,0.9982,0.0094,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9982,0.0071,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.0553,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.9865,0.0268,0.0001</t>
+  </si>
+  <si>
+    <t>0.0595,0.9387,0.0268,0.0006</t>
+  </si>
+  <si>
+    <t>0.0804,0.9221,0.0304,0.0007</t>
+  </si>
+  <si>
+    <t>0.3533,0.7151,0.0496,0.0027</t>
+  </si>
+  <si>
+    <t>0.5829,0.4794,0.0148,0.0054</t>
+  </si>
+  <si>
+    <t>0.5416,0.5572,0.0116,0.0032</t>
+  </si>
+  <si>
+    <t>0.3124,0.7609,0.0365,0.0031</t>
+  </si>
+  <si>
+    <t>0.5119,0.5889,0.0191,0.0031</t>
+  </si>
+  <si>
+    <t>0.3700,0.7143,0.0394,0.0025</t>
+  </si>
+  <si>
+    <t>0.4526,0.6561,0.0203,0.0028</t>
+  </si>
+  <si>
+    <t>0.5768,0.5281,0.0067,0.0026</t>
+  </si>
+  <si>
+    <t>0.0001,0.9951,0.2345,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9913,0.4127,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9725,0.4783,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.9336,0.5746,0.0006</t>
+  </si>
+  <si>
+    <t>0.1417,0.7410,0.1657,0.0393</t>
+  </si>
+  <si>
+    <t>0.1656,0.5088,0.4483,0.0286</t>
+  </si>
+  <si>
+    <t>0.2069,0.1616,0.6553,0.0126</t>
+  </si>
+  <si>
+    <t>0.0604,0.9020,0.0613,0.0097</t>
+  </si>
+  <si>
+    <t>0.0088,0.0130,0.0007,0.9908</t>
+  </si>
+  <si>
+    <t>0.0000,0.0054,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0462,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0020,0.0042,0.0002,0.9980</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.4337,0.0000</t>
+  </si>
+  <si>
+    <t>0.3902,0.7048,0.0127,0.0035</t>
+  </si>
+  <si>
+    <t>0.0353,0.9633,0.0085,0.0007</t>
+  </si>
+  <si>
+    <t>0.4472,0.5825,0.0246,0.0141</t>
+  </si>
+  <si>
+    <t>0.0418,0.9571,0.0133,0.0005</t>
+  </si>
+  <si>
+    <t>0.5499,0.5223,0.0146,0.0055</t>
+  </si>
+  <si>
+    <t>0.0115,0.4400,0.0030,0.9245</t>
+  </si>
+  <si>
+    <t>0.6398,0.4542,0.0149,0.0023</t>
+  </si>
+  <si>
+    <t>0.0078,0.8681,0.7103,0.0016</t>
+  </si>
+  <si>
+    <t>0.3765,0.4669,0.0081,0.0734</t>
+  </si>
+  <si>
+    <t>0.6092,0.4515,0.0121,0.0053</t>
+  </si>
+  <si>
+    <t>0.0382,0.9537,0.0188,0.0010</t>
+  </si>
+  <si>
+    <t>0.1500,0.8602,0.0310,0.0049</t>
+  </si>
+  <si>
+    <t>0.1445,0.8623,0.0416,0.0036</t>
+  </si>
+  <si>
+    <t>0.0322,0.9499,0.0302,0.0025</t>
+  </si>
+  <si>
+    <t>0.0872,0.8739,0.0903,0.0051</t>
+  </si>
+  <si>
+    <t>0.1043,0.8818,0.0515,0.0035</t>
+  </si>
+  <si>
+    <t>0.6008,0.4935,0.0151,0.0028</t>
+  </si>
+  <si>
+    <t>0.6903,0.3971,0.0099,0.0023</t>
+  </si>
+  <si>
+    <t>0.3617,0.7182,0.0341,0.0031</t>
+  </si>
+  <si>
+    <t>0.7087,0.3318,0.0088,0.0047</t>
+  </si>
+  <si>
+    <t>0.5087,0.6060,0.0122,0.0025</t>
+  </si>
+  <si>
+    <t>0.6509,0.4546,0.0091,0.0021</t>
+  </si>
+  <si>
+    <t>0.5124,0.5933,0.0223,0.0031</t>
+  </si>
+  <si>
+    <t>0.5734,0.5132,0.0116,0.0039</t>
+  </si>
+  <si>
+    <t>0.0381,0.9527,0.0242,0.0008</t>
+  </si>
+  <si>
+    <t>0.1089,0.9172,0.0127,0.0008</t>
+  </si>
+  <si>
+    <t>0.0552,0.9488,0.0143,0.0005</t>
+  </si>
+  <si>
+    <t>0.0882,0.7144,0.4828,0.0035</t>
+  </si>
+  <si>
+    <t>0.1118,0.9038,0.0260,0.0010</t>
+  </si>
+  <si>
+    <t>0.3032,0.7748,0.0218,0.0027</t>
+  </si>
+  <si>
+    <t>0.2394,0.8225,0.0216,0.0022</t>
+  </si>
+  <si>
+    <t>0.2071,0.8150,0.0553,0.0032</t>
+  </si>
+  <si>
+    <t>0.0002,0.2776,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.2349,0.7688,0.0723,0.0086</t>
+  </si>
+  <si>
+    <t>0.0003,0.5443,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9544,0.8498,0.0001</t>
+  </si>
+  <si>
+    <t>0.0417,0.2080,0.8859,0.0024</t>
+  </si>
+  <si>
+    <t>0.0017,0.9665,0.4448,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.8925,0.8772,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0074,0.9965,0.0010</t>
+  </si>
+  <si>
+    <t>0.0211,0.5704,0.8005,0.0023</t>
+  </si>
+  <si>
+    <t>0.0474,0.6480,0.6308,0.0178</t>
+  </si>
+  <si>
+    <t>0.0314,0.5940,0.7448,0.0066</t>
+  </si>
+  <si>
+    <t>0.0855,0.8670,0.0628,0.0228</t>
+  </si>
+  <si>
+    <t>0.0180,0.9012,0.3029,0.0031</t>
+  </si>
+  <si>
+    <t>0.0304,0.9187,0.1278,0.0039</t>
+  </si>
+  <si>
+    <t>0.0272,0.9291,0.1037,0.0064</t>
+  </si>
+  <si>
+    <t>0.2028,0.6323,0.1664,0.0540</t>
+  </si>
+  <si>
+    <t>0.0213,0.9542,0.0487,0.0036</t>
+  </si>
+  <si>
+    <t>0.1380,0.8922,0.0172,0.0014</t>
+  </si>
+  <si>
+    <t>0.0713,0.9333,0.0220,0.0006</t>
+  </si>
+  <si>
+    <t>0.1242,0.9012,0.0208,0.0008</t>
+  </si>
+  <si>
+    <t>0.1149,0.9133,0.0121,0.0009</t>
+  </si>
+  <si>
+    <t>0.0858,0.9297,0.0115,0.0008</t>
+  </si>
+  <si>
+    <t>0.0419,0.9018,0.1119,0.0043</t>
+  </si>
+  <si>
+    <t>0.2535,0.5205,0.2813,0.0201</t>
+  </si>
+  <si>
+    <t>0.1690,0.7278,0.0595,0.0802</t>
+  </si>
+  <si>
+    <t>0.0485,0.8466,0.1222,0.0838</t>
+  </si>
+  <si>
+    <t>0.4739,0.2098,0.2546,0.0326</t>
+  </si>
+  <si>
+    <t>0.0415,0.5678,0.6808,0.0108</t>
+  </si>
+  <si>
+    <t>0.0031,0.9573,0.3736,0.0013</t>
+  </si>
+  <si>
+    <t>0.0040,0.9284,0.5551,0.0012</t>
+  </si>
+  <si>
+    <t>0.0018,0.9787,0.2364,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9842,0.2489,0.0004</t>
+  </si>
+  <si>
+    <t>0.3489,0.7528,0.0140,0.0020</t>
+  </si>
+  <si>
+    <t>0.2971,0.7854,0.0148,0.0023</t>
+  </si>
+  <si>
+    <t>0.4013,0.7010,0.0208,0.0028</t>
+  </si>
+  <si>
+    <t>0.3138,0.7755,0.0147,0.0022</t>
+  </si>
+  <si>
+    <t>0.2524,0.8256,0.0179,0.0013</t>
+  </si>
+  <si>
+    <t>0.3833,0.7165,0.0127,0.0028</t>
+  </si>
+  <si>
+    <t>0.2996,0.7771,0.0249,0.0028</t>
+  </si>
+  <si>
+    <t>0.2908,0.7912,0.0219,0.0018</t>
+  </si>
+  <si>
+    <t>0.1336,0.4082,0.5881,0.0110</t>
+  </si>
+  <si>
+    <t>0.0703,0.8775,0.1103,0.0036</t>
+  </si>
+  <si>
+    <t>0.2390,0.6546,0.1662,0.0245</t>
+  </si>
+  <si>
+    <t>0.0014,0.1943,0.9893,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9703,0.7486,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.9295,0.5033,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.3481,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0137,0.7992,0.6396,0.0020</t>
+  </si>
+  <si>
+    <t>0.0002,0.8440,0.9752,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.8014,0.7715,0.0018</t>
+  </si>
+  <si>
+    <t>0.0209,0.6940,0.7156,0.0080</t>
+  </si>
+  <si>
+    <t>0.0946,0.6821,0.3349,0.0104</t>
+  </si>
+  <si>
+    <t>0.0854,0.7341,0.2418,0.0685</t>
+  </si>
+  <si>
+    <t>0.4180,0.2723,0.2780,0.0285</t>
+  </si>
+  <si>
+    <t>0.1635,0.8788,0.0187,0.0010</t>
+  </si>
+  <si>
+    <t>0.4226,0.6932,0.0176,0.0020</t>
+  </si>
+  <si>
+    <t>0.4662,0.6644,0.0089,0.0017</t>
+  </si>
+  <si>
+    <t>0.2797,0.8057,0.0224,0.0014</t>
+  </si>
+  <si>
+    <t>0.2932,0.7952,0.0127,0.0020</t>
+  </si>
+  <si>
+    <t>0.3258,0.7757,0.0187,0.0014</t>
+  </si>
+  <si>
+    <t>0.2841,0.8040,0.0166,0.0015</t>
+  </si>
+  <si>
+    <t>0.3003,0.7650,0.0388,0.0020</t>
+  </si>
+  <si>
+    <t>0.0056,0.9596,0.2101,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.9371,0.9276,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9721,0.7495,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.9537,0.3280,0.0012</t>
+  </si>
+  <si>
+    <t>0.0044,0.4845,0.9438,0.0019</t>
+  </si>
+  <si>
+    <t>0.0288,0.4759,0.1073,0.7709</t>
+  </si>
+  <si>
+    <t>0.1028,0.6133,0.4244,0.0310</t>
+  </si>
+  <si>
+    <t>0.0300,0.8881,0.2027,0.0132</t>
+  </si>
+  <si>
+    <t>0.4133,0.3997,0.0136,0.0891</t>
+  </si>
+  <si>
+    <t>0.0003,0.3027,0.0003,0.9965</t>
+  </si>
+  <si>
+    <t>0.0026,0.0246,0.0002,0.9960</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0470,0.8327,0.0110,0.2652</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,10 +2032,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,10 +2060,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,10 +2074,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,10 +2088,10 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,10 +2102,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>263</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>263</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2172,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,10 +2298,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,10 +2494,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>263</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>263</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2581,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,10 +2662,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,10 +2690,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>262</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>263</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>262</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>262</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>262</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,10 +3292,10 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>262</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,10 +3320,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,10 +3334,10 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>262</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>262</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,10 +3376,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,10 +3390,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,10 +3418,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,10 +3754,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>262</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,10 +3782,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>262</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>262</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,10 +3824,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>262</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>262</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>262</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>262</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,10 +4076,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,10 +4244,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>262</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,10 +4300,10 @@
         <v>259</v>
       </c>
       <c r="C169" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,10 +4314,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,10 +4328,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,10 +4342,10 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>262</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>262</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>263</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,10 +4538,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>263</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,10 +4580,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>262</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>262</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,10 +4846,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>262</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>262</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>262</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>262</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>262</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>262</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>262</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>262</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>262</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>262</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,10 +5028,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>262</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,10 +5070,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>263</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>263</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>263</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>263</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>262</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>262</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>262</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>262</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>262</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>262</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>262</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>262</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>262</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>262</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>262</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
